--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2019.xlsx
@@ -554,7 +554,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -738,7 +738,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Aysén</t>
+          <t>Aysen</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2302,7 +2302,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -3222,7 +3222,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -3728,7 +3728,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -3774,7 +3774,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3912,7 +3912,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -4234,7 +4234,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -4280,7 +4280,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -4464,7 +4464,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -4510,7 +4510,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -4648,7 +4648,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -5154,7 +5154,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -5200,7 +5200,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -5430,7 +5430,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -6166,7 +6166,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -6212,7 +6212,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -6350,7 +6350,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -6672,7 +6672,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6718,7 +6718,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -6764,7 +6764,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -6810,7 +6810,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -7178,7 +7178,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -7546,7 +7546,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -7592,7 +7592,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -7730,7 +7730,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Valparaiso</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -8512,7 +8512,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Nuble</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -10168,7 +10168,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -10490,7 +10490,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -10582,7 +10582,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Tarapacá</t>
+          <t>Tarapaca</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -10766,7 +10766,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -10812,7 +10812,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -10858,7 +10858,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -10904,7 +10904,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -10950,7 +10950,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -10996,7 +10996,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -11042,7 +11042,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -11088,7 +11088,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -11134,7 +11134,7 @@
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -11180,7 +11180,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -11226,7 +11226,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -11272,7 +11272,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -11318,7 +11318,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -11364,7 +11364,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -11548,7 +11548,7 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D244" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -11732,7 +11732,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -11778,7 +11778,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -11870,7 +11870,7 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
@@ -12008,7 +12008,7 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -12100,7 +12100,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -12238,7 +12238,7 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
@@ -12284,7 +12284,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -12330,7 +12330,7 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -12468,7 +12468,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -12514,7 +12514,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -12560,7 +12560,7 @@
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -12744,7 +12744,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -12790,7 +12790,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -12836,7 +12836,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -12928,7 +12928,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -12974,7 +12974,7 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
@@ -13020,7 +13020,7 @@
       </c>
       <c r="C276" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D276" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -13112,7 +13112,7 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -13204,7 +13204,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -13250,7 +13250,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -13296,7 +13296,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -13388,7 +13388,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -13572,7 +13572,7 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -13802,7 +13802,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -14032,7 +14032,7 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -14078,7 +14078,7 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -14124,7 +14124,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -14170,7 +14170,7 @@
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -14216,7 +14216,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -14262,7 +14262,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -14308,7 +14308,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -14446,7 +14446,7 @@
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
@@ -14492,7 +14492,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -14584,7 +14584,7 @@
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -14630,7 +14630,7 @@
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>Los Ríos</t>
+          <t>Los Rios</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
@@ -14768,7 +14768,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -14860,7 +14860,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14906,7 +14906,7 @@
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14952,7 +14952,7 @@
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
@@ -15090,7 +15090,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
@@ -15274,7 +15274,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -15412,7 +15412,7 @@
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -15458,7 +15458,7 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
@@ -15504,7 +15504,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>La Araucanía</t>
+          <t>La Araucania</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Biobio</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2019.xlsx
@@ -2101,7 +2101,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-30 15:44</t>
+    <t xml:space="preserve">2026-09-07 12:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_supneta_a_2019.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_supneta_a_2019.xlsx
@@ -2101,7 +2101,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:51</t>
+    <t xml:space="preserve">2026-09-08 10:21</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
